--- a/results/Int Task Remove ACC -0.5/Rando_9_permute.xlsx
+++ b/results/Int Task Remove ACC -0.5/Rando_9_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6672717059804194</v>
+        <v>0.6650209021218985</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6684747032114733</v>
+        <v>0.6646993587135384</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6669085743708659</v>
+        <v>0.6636515520860714</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.660570064416703</v>
+        <v>0.6644194035063715</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6551758406757813</v>
+        <v>0.6663486639565323</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6432594707676353</v>
+        <v>0.6678843667971324</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6432594707676353</v>
+        <v>0.6676044115899655</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6427715745545022</v>
+        <v>0.6644113019087364</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6226279422302078</v>
+        <v>0.6636241866896152</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6240693064672354</v>
+        <v>0.6633442314824484</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6285181637818977</v>
+        <v>0.6597960917893009</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6376014950148169</v>
+        <v>0.6658415039445779</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.635952189771823</v>
+        <v>0.6654783723350245</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.635952189771823</v>
+        <v>0.6668893105720448</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6356722345646562</v>
+        <v>0.6645441681099513</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6586793315641845</v>
+        <v>0.6638179048908445</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6585961551617978</v>
+        <v>0.6551616178710442</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6580362447474641</v>
+        <v>0.6525284186041487</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.666770667175567</v>
+        <v>0.6528499620125089</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.666770667175567</v>
+        <v>0.6531299172196757</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6588487449725086</v>
+        <v>0.632485246090529</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6620337530561027</v>
+        <v>0.6252479989053842</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6672504617910653</v>
+        <v>0.6163360614713221</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6695956042531588</v>
+        <v>0.6210537117919654</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6646943177194543</v>
+        <v>0.6190108489394108</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.665545345542141</v>
+        <v>0.6124887027721866</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6645807153170605</v>
+        <v>0.6030838281309074</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6675050319923088</v>
+        <v>0.6053873823918077</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6729793715320662</v>
+        <v>0.5972767829816039</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6495067027217767</v>
+        <v>0.6065264670192962</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.65256388559824</v>
+        <v>0.5982961439995966</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.667063764974453</v>
+        <v>0.5899887657846128</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6677819265959247</v>
+        <v>0.558915898215128</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6563727166997332</v>
+        <v>0.5919120850631745</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6568656539069504</v>
+        <v>0.588511034375979</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6655442653291229</v>
+        <v>0.5834079280434101</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6649316045124098</v>
+        <v>0.5557074855161438</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.654084285421085</v>
+        <v>0.5615672810678266</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6582836135285879</v>
+        <v>0.5626455136953007</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6440058979630783</v>
+        <v>0.571285597519831</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6401057888615636</v>
+        <v>0.5869276221270834</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6657653489268083</v>
+        <v>0.5863677117127497</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6711626332712811</v>
+        <v>0.5882573643522503</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.666331380548244</v>
+        <v>0.5942550670992319</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6876911526953116</v>
+        <v>0.5942550670992319</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6781777166457226</v>
+        <v>0.5942550670992319</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6748182541597203</v>
+        <v>0.5901531381988528</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6682595607853868</v>
+        <v>0.5901531381988528</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6682595607853868</v>
+        <v>0.5891469197725792</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6721789336857228</v>
+        <v>0.5907657990155659</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.675367002372868</v>
+        <v>0.595464185537388</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7034275159061367</v>
+        <v>0.6020309805093564</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7225537676029713</v>
+        <v>0.5913591960334579</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7093380814696658</v>
+        <v>0.5908266510155803</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7340522751086513</v>
+        <v>0.6085642888777667</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7478624384728668</v>
+        <v>0.6033029313380598</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7404496566722958</v>
+        <v>0.6346629555348314</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7388946900328746</v>
+        <v>0.6450852108035705</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7390610428376476</v>
+        <v>0.6402397352757965</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7342459933098807</v>
+        <v>0.641839350719962</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7372443045768626</v>
+        <v>0.6306126968238137</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7366732319613427</v>
+        <v>0.6306126968238137</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7124876225591686</v>
+        <v>0.6457475614191118</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.712839591967536</v>
+        <v>0.6402732218793546</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.711791785340069</v>
+        <v>0.6458946504250638</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7000295258224922</v>
+        <v>0.6320492001022602</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7000295258224922</v>
+        <v>0.6153878144770148</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7007457070534309</v>
+        <v>0.6280781570125629</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7000306060355102</v>
+        <v>0.6027473417757983</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6993875192187899</v>
+        <v>0.6030964306161175</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6738100553429136</v>
+        <v>0.5716622317921094</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6736437025381405</v>
+        <v>0.5716622317921094</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6736437025381405</v>
+        <v>0.5932745937498874</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6548278320484799</v>
+        <v>0.5606568415291495</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6228601880290794</v>
+        <v>0.5327810444219601</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6355474699610764</v>
+        <v>0.5335103682446178</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6455792282238058</v>
+        <v>0.5247231954141357</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6459007716321659</v>
+        <v>0.5229491255675619</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6330401155107788</v>
+        <v>0.5557728384037331</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6270220687519579</v>
+        <v>0.5539379165571451</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6270220687519579</v>
+        <v>0.5481035060113855</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6006718924972004</v>
+        <v>0.5486614360351861</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6099023127360715</v>
+        <v>0.5517317615033684</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5817728456051534</v>
+        <v>0.5088062565938003</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5885302981748001</v>
+        <v>0.5150565491514927</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5910245100333786</v>
+        <v>0.5143830363347652</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5818641236051749</v>
+        <v>0.5262243314381596</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5045532779064031</v>
+        <v>0.5258611998286062</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5055483341314907</v>
+        <v>0.5124892428786957</v>
       </c>
     </row>
   </sheetData>
